--- a/static/files/Targets_bulk.xlsx
+++ b/static/files/Targets_bulk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960AAF60-1BBE-45A8-B900-D0203F8364FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FC5923-14D9-4282-8438-0E5DD0760134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B78F166-9148-4A1E-B146-EAC07673DB29}"/>
   </bookViews>
@@ -111,13 +111,13 @@
     <t>Documentation Update Target</t>
   </si>
   <si>
-    <t xml:space="preserve">Research Target </t>
-  </si>
-  <si>
     <t>Target Month</t>
   </si>
   <si>
     <t>Target Year</t>
+  </si>
+  <si>
+    <t>Research Target</t>
   </si>
 </sst>
 </file>
@@ -588,14 +588,14 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/static/files/Targets_bulk.xlsx
+++ b/static/files/Targets_bulk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FC5923-14D9-4282-8438-0E5DD0760134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E1B902-BD53-4C75-8280-D4130C844F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B78F166-9148-4A1E-B146-EAC07673DB29}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,21 +133,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFA31515"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -155,18 +166,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,101 +531,101 @@
     <col min="18" max="18" width="17.5546875" customWidth="1"/>
     <col min="19" max="19" width="15.44140625" customWidth="1"/>
     <col min="20" max="20" width="16.33203125" customWidth="1"/>
-    <col min="21" max="21" width="18.77734375" customWidth="1"/>
+    <col min="21" max="21" width="20.5546875" customWidth="1"/>
     <col min="22" max="22" width="13.33203125" customWidth="1"/>
     <col min="23" max="23" width="15.21875" customWidth="1"/>
     <col min="24" max="24" width="14.21875" customWidth="1"/>
     <col min="25" max="25" width="18.33203125" customWidth="1"/>
     <col min="26" max="26" width="15.88671875" customWidth="1"/>
-    <col min="27" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="13.33203125" customWidth="1"/>
+    <col min="27" max="27" width="19.21875" customWidth="1"/>
+    <col min="28" max="28" width="19.88671875" customWidth="1"/>
     <col min="29" max="29" width="15.5546875" customWidth="1"/>
     <col min="30" max="30" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:28" s="5" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
